--- a/CRM.BITM.Vtiger/src/test/resources/TestData.xlsx
+++ b/CRM.BITM.Vtiger/src/test/resources/TestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\CRM.BITM.Vtiger\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\git\vtigerRepo\CRM.BITM.Vtiger\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5BE9B0-E1A0-46BF-ADD0-7E16A7A96E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FD69F1-0B28-4E95-BCDA-A865F84D880D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{CB9567A7-4C8E-46EA-B7A3-EA2DB94F2E41}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CB9567A7-4C8E-46EA-B7A3-EA2DB94F2E41}"/>
   </bookViews>
   <sheets>
     <sheet name="VendorData" sheetId="1" r:id="rId1"/>
@@ -205,18 +205,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -231,13 +223,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -267,33 +252,40 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -610,9 +602,9 @@
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="27.44140625" customWidth="1"/>
+    <col min="4" max="4" width="27.44140625" style="11" customWidth="1"/>
     <col min="5" max="5" width="15.109375" customWidth="1"/>
     <col min="6" max="6" width="18.33203125" customWidth="1"/>
     <col min="7" max="7" width="11.5546875" customWidth="1"/>
@@ -622,185 +614,180 @@
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="19.44140625" customWidth="1"/>
     <col min="13" max="13" width="18.33203125" customWidth="1"/>
-    <col min="14" max="14" width="19.77734375" style="7" customWidth="1"/>
+    <col min="14" max="14" width="19.77734375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="7">
         <v>9876543210</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="7">
         <v>560001</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="7" t="s">
         <v>39</v>
       </c>
+      <c r="N2" s="9"/>
     </row>
     <row r="3" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="7">
         <v>9876543211</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="7">
         <v>570001</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="7">
+      <c r="M3" s="10"/>
+      <c r="N3" s="9">
         <v>9876543288</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="7">
         <v>9876543212</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="7">
         <v>580020</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="7">
+      <c r="M4" s="10"/>
+      <c r="N4" s="9">
         <v>9876543277</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="mailto:unique01@example.com" xr:uid="{0CB6E7D7-082A-4FED-AD2E-E628DB9B1B15}"/>
-    <hyperlink ref="D2" r:id="rId2" display="https://uniquevendor01.com/" xr:uid="{29FB9871-F244-4828-A276-4A1ACD611E81}"/>
-    <hyperlink ref="B3" r:id="rId3" display="mailto:unique02@example.com" xr:uid="{8677DD77-08B2-4F3E-AB46-79B7C99DF80A}"/>
-    <hyperlink ref="D3" r:id="rId4" display="https://uniquevendor02.com/" xr:uid="{90DB4587-7BF8-42F6-ABF3-6919F91D6F4C}"/>
-    <hyperlink ref="B4" r:id="rId5" display="mailto:unique03@example.com" xr:uid="{4CE2EFC6-7468-4852-A946-FA786C03FD20}"/>
-    <hyperlink ref="D4" r:id="rId6" display="https://uniquevendor03.com/" xr:uid="{B586F23A-E4E6-4499-B7E3-52168E98231E}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -818,42 +805,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="3">
         <v>1</v>
       </c>
     </row>
@@ -872,18 +859,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
     </row>
@@ -897,34 +884,34 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" style="7" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="11.21875" style="4" customWidth="1"/>
     <col min="3" max="3" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="4" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="4" t="s">
         <v>56</v>
       </c>
     </row>

--- a/CRM.BITM.Vtiger/src/test/resources/TestData.xlsx
+++ b/CRM.BITM.Vtiger/src/test/resources/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\git\vtigerRepo\CRM.BITM.Vtiger\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FD69F1-0B28-4E95-BCDA-A865F84D880D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C54726-2607-4350-AABE-89DDE2EC5570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CB9567A7-4C8E-46EA-B7A3-EA2DB94F2E41}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{CB9567A7-4C8E-46EA-B7A3-EA2DB94F2E41}"/>
   </bookViews>
   <sheets>
     <sheet name="VendorData" sheetId="1" r:id="rId1"/>
@@ -205,7 +205,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,6 +234,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -252,10 +260,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -284,8 +293,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -665,7 +678,7 @@
       <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="7">
@@ -707,7 +720,7 @@
       <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="7">
@@ -749,7 +762,7 @@
       <c r="A4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="7">
@@ -788,6 +801,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{B1ABB738-AF15-48E6-9631-D9C40AC78853}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{8CE147D1-51A1-4D8A-9D57-8EF736808F5E}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{908250DE-A5F0-4FF2-9D06-35EA6F4CAF9D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/CRM.BITM.Vtiger/src/test/resources/TestData.xlsx
+++ b/CRM.BITM.Vtiger/src/test/resources/TestData.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\git\vtigerRepo\CRM.BITM.Vtiger\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C54726-2607-4350-AABE-89DDE2EC5570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2FA055A-99EA-406E-B636-3340A928D1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{CB9567A7-4C8E-46EA-B7A3-EA2DB94F2E41}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{CB9567A7-4C8E-46EA-B7A3-EA2DB94F2E41}"/>
   </bookViews>
   <sheets>
     <sheet name="VendorData" sheetId="1" r:id="rId1"/>
     <sheet name="PurchaseOrderData" sheetId="2" r:id="rId2"/>
     <sheet name="PriceBookData" sheetId="3" r:id="rId3"/>
     <sheet name="InvalidLogin" sheetId="4" r:id="rId4"/>
+    <sheet name="QtyBVA" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="64">
   <si>
     <t>VendorName</t>
   </si>
@@ -199,6 +200,27 @@
   </si>
   <si>
     <t>lkjhgf</t>
+  </si>
+  <si>
+    <t>ExpectedResult</t>
+  </si>
+  <si>
+    <t>Accept</t>
+  </si>
+  <si>
+    <t>Reject</t>
+  </si>
+  <si>
+    <t>BVA_PO_NEG</t>
+  </si>
+  <si>
+    <t>Bangalore</t>
+  </si>
+  <si>
+    <t>BVA_PO_ZERO</t>
+  </si>
+  <si>
+    <t>BVA_PO_MIN</t>
   </si>
 </sst>
 </file>
@@ -264,7 +286,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -295,6 +317,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -936,4 +964,101 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE773E56-3728-49E8-A733-63ABD33DA1D8}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.77734375" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="13">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="13">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>